--- a/Vulnerability Test Results/security test.xlsx
+++ b/Vulnerability Test Results/security test.xlsx
@@ -32,7 +32,7 @@
     <t>Security Audit Date</t>
   </si>
   <si>
-    <t>6/22/2026</t>
+    <t>7/20/2026</t>
   </si>
   <si>
     <t>Assessor Identity</t>

--- a/Vulnerability Test Results/security test.xlsx
+++ b/Vulnerability Test Results/security test.xlsx
@@ -32,7 +32,7 @@
     <t>Security Audit Date</t>
   </si>
   <si>
-    <t>7/20/2026</t>
+    <t>8/31/2026</t>
   </si>
   <si>
     <t>Assessor Identity</t>
